--- a/table.xlsx
+++ b/table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simim\Projekte\GitHub\Twitter bot\Twitter-bot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Projekte\GitHub\Twitter Bot\.git\Twitterbot\Twitter-bot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2939D4C-13C8-4A2C-9225-6E5010E7CE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E3FBD2-9CD3-4A01-BE11-ABF722BEB4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>Pl.</t>
   </si>
@@ -91,7 +91,7 @@
     <t>TSG Hoffenheim</t>
   </si>
   <si>
-    <t>6-1-3</t>
+    <t>6-2-3</t>
   </si>
   <si>
     <t>7.</t>
@@ -184,13 +184,16 @@
     <t>1. FSV Mainz 05</t>
   </si>
   <si>
+    <t>1-3-7</t>
+  </si>
+  <si>
+    <t>18.</t>
+  </si>
+  <si>
+    <t>1. FC Heidenheim 1846</t>
+  </si>
+  <si>
     <t>1-2-7</t>
-  </si>
-  <si>
-    <t>18.</t>
-  </si>
-  <si>
-    <t>1. FC Heidenheim 1846</t>
   </si>
 </sst>
 </file>
@@ -248,7 +251,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -279,50 +282,19 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -409,7 +381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -424,115 +396,162 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFFF5050"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -548,18 +567,18 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Image 8" descr="Picture">
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -572,10 +591,6 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4290060" y="1447800"/>
-          <a:ext cx="190500" cy="190500"/>
-        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -585,18 +600,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Image 9" descr="Picture">
+        <xdr:cNvPr id="3" name="Image 2" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -618,18 +633,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Image 10" descr="Picture">
+        <xdr:cNvPr id="4" name="Image 3" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -651,18 +666,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Image 11" descr="Picture">
+        <xdr:cNvPr id="5" name="Image 4" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -684,18 +699,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Image 12" descr="Picture">
+        <xdr:cNvPr id="6" name="Image 5" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -717,18 +732,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Image 13" descr="Picture">
+        <xdr:cNvPr id="7" name="Image 6" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -750,18 +765,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Image 14" descr="Picture">
+        <xdr:cNvPr id="8" name="Image 7" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -783,18 +798,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Image 15" descr="Picture">
+        <xdr:cNvPr id="9" name="Image 8" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -816,18 +831,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Image 16" descr="Picture">
+        <xdr:cNvPr id="10" name="Image 9" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -849,18 +864,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Image 17" descr="Picture">
+        <xdr:cNvPr id="11" name="Image 10" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -882,18 +897,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Image 18" descr="Picture">
+        <xdr:cNvPr id="12" name="Image 11" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -915,18 +930,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Image 19" descr="Picture">
+        <xdr:cNvPr id="13" name="Image 12" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -948,18 +963,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Image 20" descr="Picture">
+        <xdr:cNvPr id="14" name="Image 13" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -981,18 +996,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Image 21" descr="Picture">
+        <xdr:cNvPr id="15" name="Image 14" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1014,18 +1029,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="Image 22" descr="Picture">
+        <xdr:cNvPr id="16" name="Image 15" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1047,18 +1062,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Image 23" descr="Picture">
+        <xdr:cNvPr id="17" name="Image 16" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1080,18 +1095,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Image 24" descr="Picture">
+        <xdr:cNvPr id="18" name="Image 17" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1113,18 +1128,18 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="190500" cy="190500"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Image 25" descr="Picture">
+        <xdr:cNvPr id="19" name="Image 18" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001A000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1464,499 +1479,738 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:N41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="11.5546875" customWidth="1"/>
-    <col min="4" max="5" width="11.5546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="4.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="4.88671875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="33.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="7.44140625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="5.6640625" style="4" customWidth="1"/>
-    <col min="12" max="12" width="7" style="5" customWidth="1"/>
-    <col min="13" max="19" width="11.5546875" style="2" customWidth="1"/>
-    <col min="20" max="16384" width="11.5546875" style="2"/>
+    <col min="1" max="3" width="11.5703125" customWidth="1"/>
+    <col min="4" max="5" width="11.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="4.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="38.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" style="4" customWidth="1"/>
+    <col min="13" max="13" width="7" style="5" customWidth="1"/>
+    <col min="14" max="21" width="11.5703125" style="2" customWidth="1"/>
+    <col min="22" max="16384" width="11.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:13" ht="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="5:13" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="32"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-    </row>
-    <row r="3" spans="5:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="33"/>
+    <row r="1" spans="5:14" ht="49.9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="5:14" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="21"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="17"/>
+    </row>
+    <row r="3" spans="5:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E3" s="17"/>
       <c r="F3" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="7"/>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="7"/>
+      <c r="I3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="M3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="36"/>
-    </row>
-    <row r="4" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E4" s="33"/>
-      <c r="F4" s="11" t="s">
+      <c r="N3" s="15"/>
+    </row>
+    <row r="4" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E4" s="17"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="15"/>
+    </row>
+    <row r="5" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E5" s="17"/>
+      <c r="F5" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13" t="s">
+      <c r="G5" s="30"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="18">
+      <c r="J5" s="33">
         <v>10</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="K5" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="20">
+      <c r="L5" s="35">
         <v>29</v>
       </c>
-      <c r="L4" s="26">
+      <c r="M5" s="37">
         <v>28</v>
       </c>
-      <c r="M4" s="35"/>
-    </row>
-    <row r="5" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E5" s="33"/>
-      <c r="F5" s="14" t="s">
+      <c r="N5" s="24"/>
+    </row>
+    <row r="6" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E6" s="17"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="24"/>
+    </row>
+    <row r="7" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="17"/>
+      <c r="F7" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="16" t="s">
+      <c r="G7" s="23"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="21">
+      <c r="J7" s="57">
         <v>10</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="K7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="23">
+      <c r="L7" s="13">
         <v>7</v>
       </c>
-      <c r="L5" s="27">
+      <c r="M7" s="14">
         <v>22</v>
       </c>
-      <c r="M5" s="35"/>
-    </row>
-    <row r="6" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E6" s="33"/>
-      <c r="F6" s="11" t="s">
+      <c r="N7" s="38"/>
+    </row>
+    <row r="8" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="17"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="45"/>
+      <c r="N8" s="38"/>
+    </row>
+    <row r="9" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="17"/>
+      <c r="F9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="13" t="s">
+      <c r="G9" s="39"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="18">
+      <c r="J9" s="42">
         <v>10</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="K9" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="20">
+      <c r="L9" s="44">
         <v>9</v>
       </c>
-      <c r="L6" s="26">
+      <c r="M9" s="45">
         <v>21</v>
       </c>
-      <c r="M6" s="35"/>
-    </row>
-    <row r="7" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E7" s="33"/>
-      <c r="F7" s="14" t="s">
+      <c r="N9" s="38"/>
+    </row>
+    <row r="10" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="17"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="45"/>
+      <c r="N10" s="38"/>
+    </row>
+    <row r="11" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E11" s="17"/>
+      <c r="F11" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16" t="s">
+      <c r="G11" s="39"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="21">
+      <c r="J11" s="42">
         <v>10</v>
       </c>
-      <c r="J7" s="22" t="s">
+      <c r="K11" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="23">
+      <c r="L11" s="44">
         <v>5</v>
       </c>
-      <c r="L7" s="27">
+      <c r="M11" s="45">
         <v>21</v>
       </c>
-      <c r="M7" s="35"/>
-    </row>
-    <row r="8" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E8" s="33"/>
-      <c r="F8" s="11" t="s">
+      <c r="N11" s="38"/>
+    </row>
+    <row r="12" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="17"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="38"/>
+    </row>
+    <row r="13" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="17"/>
+      <c r="F13" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="13" t="s">
+      <c r="G13" s="39"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="18">
+      <c r="J13" s="42">
         <v>10</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="K13" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="K8" s="20">
+      <c r="L13" s="44">
         <v>10</v>
       </c>
-      <c r="L8" s="26">
+      <c r="M13" s="45">
         <v>20</v>
       </c>
-      <c r="M8" s="35"/>
-    </row>
-    <row r="9" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E9" s="33"/>
-      <c r="F9" s="14" t="s">
+      <c r="N13" s="38"/>
+    </row>
+    <row r="14" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="17"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="45"/>
+      <c r="N14" s="38"/>
+    </row>
+    <row r="15" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E15" s="17"/>
+      <c r="F15" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16" t="s">
+      <c r="G15" s="39"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="21">
+      <c r="J15" s="42">
+        <v>11</v>
+      </c>
+      <c r="K15" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="44">
+        <v>5</v>
+      </c>
+      <c r="M15" s="45">
+        <v>20</v>
+      </c>
+      <c r="N15" s="38"/>
+    </row>
+    <row r="16" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E16" s="17"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="45"/>
+      <c r="N16" s="38"/>
+    </row>
+    <row r="17" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E17" s="17"/>
+      <c r="F17" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="39"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" s="42">
         <v>10</v>
       </c>
-      <c r="J9" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="23">
+      <c r="K17" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="44">
+        <v>4</v>
+      </c>
+      <c r="M17" s="45">
+        <v>17</v>
+      </c>
+      <c r="N17" s="38"/>
+    </row>
+    <row r="18" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="17"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="44"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="38"/>
+    </row>
+    <row r="19" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="17"/>
+      <c r="F19" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="39"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="42">
+        <v>10</v>
+      </c>
+      <c r="K19" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="L19" s="44">
+        <v>-3</v>
+      </c>
+      <c r="M19" s="45">
+        <v>15</v>
+      </c>
+      <c r="N19" s="38"/>
+    </row>
+    <row r="20" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E20" s="17"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="38"/>
+    </row>
+    <row r="21" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E21" s="17"/>
+      <c r="F21" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="39"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" s="42">
+        <v>10</v>
+      </c>
+      <c r="K21" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" s="44">
+        <v>2</v>
+      </c>
+      <c r="M21" s="45">
+        <v>14</v>
+      </c>
+      <c r="N21" s="38"/>
+    </row>
+    <row r="22" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E22" s="17"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="44"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="38"/>
+    </row>
+    <row r="23" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E23" s="17"/>
+      <c r="F23" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="39"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="J23" s="42">
+        <v>10</v>
+      </c>
+      <c r="K23" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="L23" s="44">
+        <v>-1</v>
+      </c>
+      <c r="M23" s="45">
+        <v>13</v>
+      </c>
+      <c r="N23" s="38"/>
+    </row>
+    <row r="24" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="17"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="44"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="38"/>
+    </row>
+    <row r="25" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E25" s="17"/>
+      <c r="F25" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="G25" s="39"/>
+      <c r="H25" s="40"/>
+      <c r="I25" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="J25" s="42">
+        <v>10</v>
+      </c>
+      <c r="K25" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="L25" s="44">
+        <v>-4</v>
+      </c>
+      <c r="M25" s="45">
+        <v>12</v>
+      </c>
+      <c r="N25" s="38"/>
+    </row>
+    <row r="26" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="17"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="39"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="38"/>
+    </row>
+    <row r="27" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E27" s="17"/>
+      <c r="F27" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" s="39"/>
+      <c r="H27" s="40"/>
+      <c r="I27" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="J27" s="42">
+        <v>10</v>
+      </c>
+      <c r="K27" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="L27" s="44">
+        <v>-6</v>
+      </c>
+      <c r="M27" s="45">
+        <v>9</v>
+      </c>
+      <c r="N27" s="38"/>
+    </row>
+    <row r="28" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E28" s="17"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="44"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="38"/>
+    </row>
+    <row r="29" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E29" s="17"/>
+      <c r="F29" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29" s="39"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="J29" s="42">
+        <v>10</v>
+      </c>
+      <c r="K29" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="L29" s="44">
+        <v>-7</v>
+      </c>
+      <c r="M29" s="45">
+        <v>9</v>
+      </c>
+      <c r="N29" s="38"/>
+    </row>
+    <row r="30" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E30" s="17"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="45"/>
+      <c r="N30" s="38"/>
+    </row>
+    <row r="31" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E31" s="17"/>
+      <c r="F31" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" s="39"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="J31" s="42">
+        <v>10</v>
+      </c>
+      <c r="K31" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="L31" s="44">
+        <v>-6</v>
+      </c>
+      <c r="M31" s="45">
+        <v>8</v>
+      </c>
+      <c r="N31" s="38"/>
+    </row>
+    <row r="32" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E32" s="17"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="45"/>
+      <c r="N32" s="38"/>
+    </row>
+    <row r="33" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E33" s="17"/>
+      <c r="F33" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="G33" s="39"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="J33" s="42">
+        <v>10</v>
+      </c>
+      <c r="K33" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="44">
+        <v>-10</v>
+      </c>
+      <c r="M33" s="45">
+        <v>7</v>
+      </c>
+      <c r="N33" s="38"/>
+    </row>
+    <row r="34" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E34" s="17"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="44"/>
+      <c r="M34" s="45"/>
+      <c r="N34" s="38"/>
+    </row>
+    <row r="35" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E35" s="17"/>
+      <c r="F35" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="G35" s="39"/>
+      <c r="H35" s="40"/>
+      <c r="I35" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="J35" s="42">
+        <v>10</v>
+      </c>
+      <c r="K35" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="44">
+        <v>-11</v>
+      </c>
+      <c r="M35" s="45">
+        <v>7</v>
+      </c>
+      <c r="N35" s="38"/>
+    </row>
+    <row r="36" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E36" s="17"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="45"/>
+      <c r="N36" s="38"/>
+    </row>
+    <row r="37" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E37" s="17"/>
+      <c r="F37" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="39"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="J37" s="42">
+        <v>11</v>
+      </c>
+      <c r="K37" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="L37" s="44">
+        <v>-8</v>
+      </c>
+      <c r="M37" s="45">
+        <v>6</v>
+      </c>
+      <c r="N37" s="38"/>
+    </row>
+    <row r="38" spans="5:14" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E38" s="17"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="44"/>
+      <c r="M38" s="45"/>
+      <c r="N38" s="38"/>
+    </row>
+    <row r="39" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E39" s="17"/>
+      <c r="F39" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="G39" s="39"/>
+      <c r="H39" s="46"/>
+      <c r="I39" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="J39" s="42">
+        <v>10</v>
+      </c>
+      <c r="K39" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="L39" s="44">
+        <v>-15</v>
+      </c>
+      <c r="M39" s="45">
         <v>5</v>
       </c>
-      <c r="L9" s="27">
-        <v>19</v>
-      </c>
-      <c r="M9" s="35"/>
-    </row>
-    <row r="10" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E10" s="33"/>
-      <c r="F10" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="18">
-        <v>10</v>
-      </c>
-      <c r="J10" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" s="20">
-        <v>4</v>
-      </c>
-      <c r="L10" s="26">
-        <v>17</v>
-      </c>
-      <c r="M10" s="35"/>
-    </row>
-    <row r="11" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E11" s="33"/>
-      <c r="F11" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="21">
-        <v>10</v>
-      </c>
-      <c r="J11" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11" s="23">
-        <v>-3</v>
-      </c>
-      <c r="L11" s="27">
-        <v>15</v>
-      </c>
-      <c r="M11" s="35"/>
-    </row>
-    <row r="12" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E12" s="33"/>
-      <c r="F12" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="18">
-        <v>10</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12" s="20">
-        <v>2</v>
-      </c>
-      <c r="L12" s="26">
-        <v>14</v>
-      </c>
-      <c r="M12" s="35"/>
-    </row>
-    <row r="13" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E13" s="33"/>
-      <c r="F13" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="21">
-        <v>10</v>
-      </c>
-      <c r="J13" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="K13" s="23">
-        <v>-1</v>
-      </c>
-      <c r="L13" s="27">
-        <v>13</v>
-      </c>
-      <c r="M13" s="35"/>
-    </row>
-    <row r="14" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E14" s="33"/>
-      <c r="F14" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14" s="18">
-        <v>10</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" s="20">
-        <v>-4</v>
-      </c>
-      <c r="L14" s="26">
-        <v>12</v>
-      </c>
-      <c r="M14" s="35"/>
-    </row>
-    <row r="15" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E15" s="33"/>
-      <c r="F15" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="I15" s="21">
-        <v>10</v>
-      </c>
-      <c r="J15" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="K15" s="23">
-        <v>-6</v>
-      </c>
-      <c r="L15" s="27">
-        <v>9</v>
-      </c>
-      <c r="M15" s="35"/>
-    </row>
-    <row r="16" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E16" s="33"/>
-      <c r="F16" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="12"/>
-      <c r="H16" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="18">
-        <v>10</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" s="20">
-        <v>-7</v>
-      </c>
-      <c r="L16" s="26">
-        <v>9</v>
-      </c>
-      <c r="M16" s="35"/>
-    </row>
-    <row r="17" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E17" s="33"/>
-      <c r="F17" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="21">
-        <v>10</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="K17" s="23">
-        <v>-6</v>
-      </c>
-      <c r="L17" s="27">
-        <v>8</v>
-      </c>
-      <c r="M17" s="35"/>
-    </row>
-    <row r="18" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E18" s="33"/>
-      <c r="F18" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" s="12"/>
-      <c r="H18" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I18" s="18">
-        <v>10</v>
-      </c>
-      <c r="J18" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="K18" s="20">
-        <v>-10</v>
-      </c>
-      <c r="L18" s="26">
-        <v>7</v>
-      </c>
-      <c r="M18" s="35"/>
-    </row>
-    <row r="19" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E19" s="33"/>
-      <c r="F19" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="I19" s="21">
-        <v>10</v>
-      </c>
-      <c r="J19" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="K19" s="23">
-        <v>-11</v>
-      </c>
-      <c r="L19" s="27">
-        <v>7</v>
-      </c>
-      <c r="M19" s="35"/>
-    </row>
-    <row r="20" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E20" s="33"/>
-      <c r="F20" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20" s="12"/>
-      <c r="H20" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="I20" s="18">
-        <v>10</v>
-      </c>
-      <c r="J20" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="K20" s="20">
-        <v>-8</v>
-      </c>
-      <c r="L20" s="26">
-        <v>5</v>
-      </c>
-      <c r="M20" s="35"/>
-    </row>
-    <row r="21" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E21" s="33"/>
-      <c r="F21" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21" s="29"/>
-      <c r="H21" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="I21" s="31">
-        <v>10</v>
-      </c>
-      <c r="J21" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="K21" s="25">
-        <v>-15</v>
-      </c>
-      <c r="L21" s="28">
-        <v>5</v>
-      </c>
-      <c r="M21" s="35"/>
-    </row>
-    <row r="22" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E22" s="33"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="33"/>
-    </row>
-    <row r="23" spans="5:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E23" s="33"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="33"/>
+      <c r="N39" s="38"/>
+    </row>
+    <row r="40" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E40" s="17"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="20"/>
+      <c r="N40" s="17"/>
+    </row>
+    <row r="41" spans="5:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E41" s="17"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="E2:E23"/>
-    <mergeCell ref="F22:M23"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="M4:M21"/>
+    <mergeCell ref="F2:N2"/>
+    <mergeCell ref="N5:N39"/>
+    <mergeCell ref="E2:E41"/>
+    <mergeCell ref="F40:N41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/table.xlsx
+++ b/table.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabelle1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -718,12 +718,12 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -733,13 +733,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -748,7 +748,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -758,13 +758,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -773,7 +773,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -783,13 +783,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -798,7 +798,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -808,13 +808,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -823,7 +823,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -833,13 +833,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -848,7 +848,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -858,13 +858,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -873,7 +873,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -883,13 +883,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -898,7 +898,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>17</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -908,13 +908,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -923,7 +923,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -933,13 +933,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -948,7 +948,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -958,13 +958,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -973,7 +973,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -983,13 +983,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -998,7 +998,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -1008,13 +1008,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1023,7 +1023,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>27</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -1033,13 +1033,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1048,7 +1048,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -1058,13 +1058,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1073,7 +1073,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -1083,13 +1083,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1098,7 +1098,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -1108,13 +1108,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1123,7 +1123,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -1133,13 +1133,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1148,7 +1148,7 @@
     <from>
       <col>6</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="190500" cy="190500"/>
@@ -1158,13 +1158,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1574,11 +1574,25 @@
         </is>
       </c>
       <c r="G4" s="8" t="n"/>
-      <c r="H4" s="8" t="n"/>
-      <c r="I4" s="62" t="n"/>
-      <c r="J4" s="63" t="n"/>
-      <c r="K4" s="64" t="n"/>
-      <c r="L4" s="57" t="n"/>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>FC Bayern München</t>
+        </is>
+      </c>
+      <c r="I4" s="62" t="n">
+        <v>12</v>
+      </c>
+      <c r="J4" s="63" t="inlineStr">
+        <is>
+          <t>11-1-0</t>
+        </is>
+      </c>
+      <c r="K4" s="64" t="n">
+        <v>35</v>
+      </c>
+      <c r="L4" s="57" t="n">
+        <v>34</v>
+      </c>
       <c r="M4" s="7" t="n"/>
       <c r="N4" s="7" t="n"/>
     </row>
@@ -1618,11 +1632,25 @@
         </is>
       </c>
       <c r="G6" s="11" t="n"/>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="68" t="n"/>
-      <c r="J6" s="69" t="n"/>
-      <c r="K6" s="70" t="n"/>
-      <c r="L6" s="42" t="n"/>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I6" s="68" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" s="69" t="inlineStr">
+        <is>
+          <t>8-2-2</t>
+        </is>
+      </c>
+      <c r="K6" s="70" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" s="42" t="n">
+        <v>26</v>
+      </c>
       <c r="N6" s="7" t="n"/>
     </row>
     <row r="7" ht="19.9" customHeight="1">
@@ -1660,11 +1688,25 @@
         </is>
       </c>
       <c r="G8" s="11" t="n"/>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="68" t="n"/>
-      <c r="J8" s="69" t="n"/>
-      <c r="K8" s="70" t="n"/>
-      <c r="L8" s="42" t="n"/>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="I8" s="68" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" s="69" t="inlineStr">
+        <is>
+          <t>7-4-1</t>
+        </is>
+      </c>
+      <c r="K8" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" s="42" t="n">
+        <v>25</v>
+      </c>
       <c r="N8" s="7" t="n"/>
     </row>
     <row r="9" ht="19.9" customHeight="1">
@@ -1702,11 +1744,25 @@
         </is>
       </c>
       <c r="G10" s="11" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="68" t="n"/>
-      <c r="J10" s="69" t="n"/>
-      <c r="K10" s="70" t="n"/>
-      <c r="L10" s="42" t="n"/>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>Bayer 04 Leverkusen</t>
+        </is>
+      </c>
+      <c r="I10" s="68" t="n">
+        <v>12</v>
+      </c>
+      <c r="J10" s="69" t="inlineStr">
+        <is>
+          <t>7-2-3</t>
+        </is>
+      </c>
+      <c r="K10" s="70" t="n">
+        <v>11</v>
+      </c>
+      <c r="L10" s="42" t="n">
+        <v>23</v>
+      </c>
       <c r="N10" s="7" t="n"/>
     </row>
     <row r="11" ht="19.9" customHeight="1">
@@ -1744,11 +1800,25 @@
         </is>
       </c>
       <c r="G12" s="15" t="n"/>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="74" t="n"/>
-      <c r="J12" s="75" t="n"/>
-      <c r="K12" s="76" t="n"/>
-      <c r="L12" s="44" t="n"/>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>TSG Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I12" s="74" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" s="75" t="inlineStr">
+        <is>
+          <t>7-2-3</t>
+        </is>
+      </c>
+      <c r="K12" s="76" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" s="44" t="n">
+        <v>23</v>
+      </c>
       <c r="N12" s="7" t="n"/>
     </row>
     <row r="13" ht="19.9" customHeight="1">
@@ -1786,11 +1856,25 @@
         </is>
       </c>
       <c r="G14" s="19" t="n"/>
-      <c r="H14" s="20" t="n"/>
-      <c r="I14" s="80" t="n"/>
-      <c r="J14" s="81" t="n"/>
-      <c r="K14" s="82" t="n"/>
-      <c r="L14" s="46" t="n"/>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>VfB Stuttgart</t>
+        </is>
+      </c>
+      <c r="I14" s="80" t="n">
+        <v>12</v>
+      </c>
+      <c r="J14" s="81" t="inlineStr">
+        <is>
+          <t>7-1-4</t>
+        </is>
+      </c>
+      <c r="K14" s="82" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="46" t="n">
+        <v>22</v>
+      </c>
       <c r="N14" s="7" t="n"/>
     </row>
     <row r="15" ht="19.9" customHeight="1">
@@ -1828,11 +1912,25 @@
         </is>
       </c>
       <c r="G16" s="23" t="n"/>
-      <c r="H16" s="24" t="n"/>
-      <c r="I16" s="86" t="n"/>
-      <c r="J16" s="87" t="n"/>
-      <c r="K16" s="88" t="n"/>
-      <c r="L16" s="48" t="n"/>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I16" s="86" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" s="87" t="inlineStr">
+        <is>
+          <t>6-3-3</t>
+        </is>
+      </c>
+      <c r="K16" s="88" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" s="48" t="n">
+        <v>21</v>
+      </c>
       <c r="N16" s="7" t="n"/>
     </row>
     <row r="17" ht="19.9" customHeight="1">
@@ -1870,11 +1968,25 @@
         </is>
       </c>
       <c r="G18" s="27" t="n"/>
-      <c r="H18" s="28" t="n"/>
-      <c r="I18" s="92" t="n"/>
-      <c r="J18" s="93" t="n"/>
-      <c r="K18" s="94" t="n"/>
-      <c r="L18" s="50" t="n"/>
+      <c r="H18" s="28" t="inlineStr">
+        <is>
+          <t>SC Freiburg</t>
+        </is>
+      </c>
+      <c r="I18" s="92" t="n">
+        <v>12</v>
+      </c>
+      <c r="J18" s="93" t="inlineStr">
+        <is>
+          <t>4-4-4</t>
+        </is>
+      </c>
+      <c r="K18" s="94" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L18" s="50" t="n">
+        <v>16</v>
+      </c>
       <c r="N18" s="7" t="n"/>
     </row>
     <row r="19" ht="19.9" customHeight="1">
@@ -1912,11 +2024,25 @@
         </is>
       </c>
       <c r="G20" s="23" t="n"/>
-      <c r="H20" s="24" t="n"/>
-      <c r="I20" s="86" t="n"/>
-      <c r="J20" s="87" t="n"/>
-      <c r="K20" s="88" t="n"/>
-      <c r="L20" s="48" t="n"/>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>SV Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I20" s="86" t="n">
+        <v>12</v>
+      </c>
+      <c r="J20" s="87" t="inlineStr">
+        <is>
+          <t>4-4-4</t>
+        </is>
+      </c>
+      <c r="K20" s="88" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L20" s="48" t="n">
+        <v>16</v>
+      </c>
       <c r="N20" s="7" t="n"/>
     </row>
     <row r="21" ht="19.9" customHeight="1">
@@ -1954,11 +2080,25 @@
         </is>
       </c>
       <c r="G22" s="27" t="n"/>
-      <c r="H22" s="28" t="n"/>
-      <c r="I22" s="92" t="n"/>
-      <c r="J22" s="93" t="n"/>
-      <c r="K22" s="94" t="n"/>
-      <c r="L22" s="50" t="n"/>
+      <c r="H22" s="28" t="inlineStr">
+        <is>
+          <t>1. FC Köln</t>
+        </is>
+      </c>
+      <c r="I22" s="92" t="n">
+        <v>12</v>
+      </c>
+      <c r="J22" s="93" t="inlineStr">
+        <is>
+          <t>4-3-5</t>
+        </is>
+      </c>
+      <c r="K22" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="50" t="n">
+        <v>15</v>
+      </c>
       <c r="N22" s="7" t="n"/>
     </row>
     <row r="23" ht="19.9" customHeight="1">
@@ -1996,11 +2136,25 @@
         </is>
       </c>
       <c r="G24" s="23" t="n"/>
-      <c r="H24" s="24" t="n"/>
-      <c r="I24" s="86" t="n"/>
-      <c r="J24" s="87" t="n"/>
-      <c r="K24" s="88" t="n"/>
-      <c r="L24" s="48" t="n"/>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>1. FC Union Berlin</t>
+        </is>
+      </c>
+      <c r="I24" s="86" t="n">
+        <v>12</v>
+      </c>
+      <c r="J24" s="87" t="inlineStr">
+        <is>
+          <t>4-3-5</t>
+        </is>
+      </c>
+      <c r="K24" s="88" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L24" s="48" t="n">
+        <v>15</v>
+      </c>
       <c r="N24" s="7" t="n"/>
     </row>
     <row r="25" ht="19.9" customHeight="1">
@@ -2038,11 +2192,25 @@
         </is>
       </c>
       <c r="G26" s="27" t="n"/>
-      <c r="H26" s="28" t="n"/>
-      <c r="I26" s="92" t="n"/>
-      <c r="J26" s="93" t="n"/>
-      <c r="K26" s="94" t="n"/>
-      <c r="L26" s="50" t="n"/>
+      <c r="H26" s="28" t="inlineStr">
+        <is>
+          <t>Borussia Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="I26" s="92" t="n">
+        <v>12</v>
+      </c>
+      <c r="J26" s="93" t="inlineStr">
+        <is>
+          <t>3-4-5</t>
+        </is>
+      </c>
+      <c r="K26" s="94" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L26" s="50" t="n">
+        <v>13</v>
+      </c>
       <c r="N26" s="7" t="n"/>
     </row>
     <row r="27" ht="19.9" customHeight="1">
@@ -2080,11 +2248,25 @@
         </is>
       </c>
       <c r="G28" s="23" t="n"/>
-      <c r="H28" s="24" t="n"/>
-      <c r="I28" s="86" t="n"/>
-      <c r="J28" s="87" t="n"/>
-      <c r="K28" s="88" t="n"/>
-      <c r="L28" s="48" t="n"/>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="I28" s="86" t="n">
+        <v>12</v>
+      </c>
+      <c r="J28" s="87" t="inlineStr">
+        <is>
+          <t>3-3-6</t>
+        </is>
+      </c>
+      <c r="K28" s="88" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L28" s="48" t="n">
+        <v>12</v>
+      </c>
       <c r="N28" s="7" t="n"/>
     </row>
     <row r="29" ht="19.9" customHeight="1">
@@ -2122,11 +2304,25 @@
         </is>
       </c>
       <c r="G30" s="27" t="n"/>
-      <c r="H30" s="28" t="n"/>
-      <c r="I30" s="92" t="n"/>
-      <c r="J30" s="93" t="n"/>
-      <c r="K30" s="94" t="n"/>
-      <c r="L30" s="50" t="n"/>
+      <c r="H30" s="28" t="inlineStr">
+        <is>
+          <t>FC Augsburg</t>
+        </is>
+      </c>
+      <c r="I30" s="92" t="n">
+        <v>12</v>
+      </c>
+      <c r="J30" s="93" t="inlineStr">
+        <is>
+          <t>3-1-8</t>
+        </is>
+      </c>
+      <c r="K30" s="94" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L30" s="50" t="n">
+        <v>10</v>
+      </c>
       <c r="N30" s="7" t="n"/>
     </row>
     <row r="31" ht="19.9" customHeight="1">
@@ -2164,11 +2360,25 @@
         </is>
       </c>
       <c r="G32" s="23" t="n"/>
-      <c r="H32" s="24" t="n"/>
-      <c r="I32" s="86" t="n"/>
-      <c r="J32" s="87" t="n"/>
-      <c r="K32" s="88" t="n"/>
-      <c r="L32" s="48" t="n"/>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>VfL Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I32" s="86" t="n">
+        <v>12</v>
+      </c>
+      <c r="J32" s="87" t="inlineStr">
+        <is>
+          <t>2-3-7</t>
+        </is>
+      </c>
+      <c r="K32" s="88" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L32" s="48" t="n">
+        <v>9</v>
+      </c>
       <c r="N32" s="7" t="n"/>
     </row>
     <row r="33" ht="19.9" customHeight="1">
@@ -2206,11 +2416,25 @@
         </is>
       </c>
       <c r="G34" s="31" t="n"/>
-      <c r="H34" s="32" t="n"/>
-      <c r="I34" s="98" t="n"/>
-      <c r="J34" s="99" t="n"/>
-      <c r="K34" s="100" t="n"/>
-      <c r="L34" s="52" t="n"/>
+      <c r="H34" s="32" t="inlineStr">
+        <is>
+          <t>1. FC Heidenheim 1846</t>
+        </is>
+      </c>
+      <c r="I34" s="98" t="n">
+        <v>12</v>
+      </c>
+      <c r="J34" s="99" t="inlineStr">
+        <is>
+          <t>2-2-8</t>
+        </is>
+      </c>
+      <c r="K34" s="100" t="n">
+        <v>-17</v>
+      </c>
+      <c r="L34" s="52" t="n">
+        <v>8</v>
+      </c>
       <c r="N34" s="7" t="n"/>
     </row>
     <row r="35" ht="19.9" customHeight="1">
@@ -2248,11 +2472,25 @@
         </is>
       </c>
       <c r="G36" s="35" t="n"/>
-      <c r="H36" s="36" t="n"/>
-      <c r="I36" s="104" t="n"/>
-      <c r="J36" s="105" t="n"/>
-      <c r="K36" s="106" t="n"/>
-      <c r="L36" s="54" t="n"/>
+      <c r="H36" s="36" t="inlineStr">
+        <is>
+          <t>FC St. Pauli</t>
+        </is>
+      </c>
+      <c r="I36" s="104" t="n">
+        <v>12</v>
+      </c>
+      <c r="J36" s="105" t="inlineStr">
+        <is>
+          <t>2-1-9</t>
+        </is>
+      </c>
+      <c r="K36" s="106" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L36" s="54" t="n">
+        <v>7</v>
+      </c>
       <c r="N36" s="7" t="n"/>
     </row>
     <row r="37" ht="19.9" customHeight="1">
@@ -2290,11 +2528,25 @@
         </is>
       </c>
       <c r="G38" s="35" t="n"/>
-      <c r="H38" s="36" t="n"/>
-      <c r="I38" s="104" t="n"/>
-      <c r="J38" s="105" t="n"/>
-      <c r="K38" s="106" t="n"/>
-      <c r="L38" s="54" t="n"/>
+      <c r="H38" s="36" t="inlineStr">
+        <is>
+          <t>1. FSV Mainz 05</t>
+        </is>
+      </c>
+      <c r="I38" s="104" t="n">
+        <v>12</v>
+      </c>
+      <c r="J38" s="105" t="inlineStr">
+        <is>
+          <t>1-3-8</t>
+        </is>
+      </c>
+      <c r="K38" s="106" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L38" s="54" t="n">
+        <v>6</v>
+      </c>
       <c r="N38" s="7" t="n"/>
     </row>
     <row r="39" ht="19.9" customHeight="1">

--- a/table.xlsx
+++ b/table.xlsx
@@ -1593,18 +1593,18 @@
         </is>
       </c>
       <c r="I5" s="65" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J5" s="66" t="inlineStr">
         <is>
-          <t>11-1-0</t>
+          <t>12-1-0</t>
         </is>
       </c>
       <c r="K5" s="67" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L5" s="41" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M5" s="110" t="n"/>
       <c r="N5" s="7" t="n"/>
@@ -1636,18 +1636,18 @@
         </is>
       </c>
       <c r="I7" s="71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" s="72" t="inlineStr">
         <is>
-          <t>8-2-2</t>
+          <t>9-2-2</t>
         </is>
       </c>
       <c r="K7" s="73" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L7" s="43" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="N7" s="7" t="n"/>
     </row>
@@ -1678,18 +1678,18 @@
         </is>
       </c>
       <c r="I9" s="71" t="n">
+        <v>13</v>
+      </c>
+      <c r="J9" s="72" t="inlineStr">
+        <is>
+          <t>8-4-1</t>
+        </is>
+      </c>
+      <c r="K9" s="73" t="n">
         <v>12</v>
       </c>
-      <c r="J9" s="72" t="inlineStr">
-        <is>
-          <t>7-4-1</t>
-        </is>
-      </c>
-      <c r="K9" s="73" t="n">
-        <v>10</v>
-      </c>
       <c r="L9" s="43" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N9" s="7" t="n"/>
     </row>
@@ -1720,15 +1720,15 @@
         </is>
       </c>
       <c r="I11" s="71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J11" s="72" t="inlineStr">
         <is>
-          <t>7-2-3</t>
+          <t>7-2-4</t>
         </is>
       </c>
       <c r="K11" s="73" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L11" s="43" t="n">
         <v>23</v>
@@ -1762,15 +1762,15 @@
         </is>
       </c>
       <c r="I13" s="77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J13" s="78" t="inlineStr">
         <is>
-          <t>7-2-3</t>
+          <t>7-2-4</t>
         </is>
       </c>
       <c r="K13" s="79" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L13" s="45" t="n">
         <v>23</v>
@@ -1804,15 +1804,15 @@
         </is>
       </c>
       <c r="I15" s="83" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J15" s="84" t="inlineStr">
         <is>
-          <t>7-1-3</t>
+          <t>7-1-5</t>
         </is>
       </c>
       <c r="K15" s="85" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L15" s="47" t="n">
         <v>22</v>
@@ -1846,18 +1846,18 @@
         </is>
       </c>
       <c r="I17" s="89" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J17" s="90" t="inlineStr">
         <is>
-          <t>6-2-3</t>
+          <t>6-3-4</t>
         </is>
       </c>
       <c r="K17" s="91" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L17" s="49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N17" s="7" t="n"/>
     </row>
@@ -1884,19 +1884,19 @@
       <c r="G19" s="29" t="n"/>
       <c r="H19" s="30" t="inlineStr">
         <is>
-          <t>SV Werder Bremen</t>
+          <t>1. FC Köln</t>
         </is>
       </c>
       <c r="I19" s="95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J19" s="96" t="inlineStr">
         <is>
-          <t>4-4-4</t>
+          <t>4-4-5</t>
         </is>
       </c>
       <c r="K19" s="97" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="L19" s="51" t="n">
         <v>16</v>
@@ -1926,22 +1926,22 @@
       <c r="G21" s="25" t="n"/>
       <c r="H21" s="26" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>SC Freiburg</t>
         </is>
       </c>
       <c r="I21" s="89" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J21" s="90" t="inlineStr">
         <is>
-          <t>4-3-5</t>
+          <t>4-4-5</t>
         </is>
       </c>
       <c r="K21" s="91" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L21" s="49" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N21" s="7" t="n"/>
     </row>
@@ -1968,22 +1968,22 @@
       <c r="G23" s="29" t="n"/>
       <c r="H23" s="30" t="inlineStr">
         <is>
-          <t>1. FC Union Berlin</t>
+          <t>Borussia Mönchengladbach</t>
         </is>
       </c>
       <c r="I23" s="95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J23" s="96" t="inlineStr">
         <is>
-          <t>4-3-5</t>
+          <t>4-4-5</t>
         </is>
       </c>
       <c r="K23" s="97" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L23" s="51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N23" s="7" t="n"/>
     </row>
@@ -2010,22 +2010,22 @@
       <c r="G25" s="25" t="n"/>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>Borussia Mönchengladbach</t>
+          <t>SV Werder Bremen</t>
         </is>
       </c>
       <c r="I25" s="89" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J25" s="90" t="inlineStr">
         <is>
-          <t>3-4-5</t>
+          <t>4-4-5</t>
         </is>
       </c>
       <c r="K25" s="91" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="L25" s="49" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N25" s="7" t="n"/>
     </row>
@@ -2052,22 +2052,22 @@
       <c r="G27" s="29" t="n"/>
       <c r="H27" s="30" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>1. FC Union Berlin</t>
         </is>
       </c>
       <c r="I27" s="95" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J27" s="96" t="inlineStr">
         <is>
-          <t>3-4-4</t>
+          <t>4-3-6</t>
         </is>
       </c>
       <c r="K27" s="97" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="L27" s="51" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N27" s="7" t="n"/>
     </row>
@@ -2094,22 +2094,22 @@
       <c r="G29" s="25" t="n"/>
       <c r="H29" s="26" t="inlineStr">
         <is>
-          <t>FC Augsburg</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="I29" s="89" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J29" s="90" t="inlineStr">
         <is>
-          <t>3-1-8</t>
+          <t>4-3-6</t>
         </is>
       </c>
       <c r="K29" s="91" t="n">
-        <v>-12</v>
+        <v>-6</v>
       </c>
       <c r="L29" s="49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N29" s="7" t="n"/>
     </row>
@@ -2136,22 +2136,22 @@
       <c r="G31" s="29" t="n"/>
       <c r="H31" s="30" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>FC Augsburg</t>
         </is>
       </c>
       <c r="I31" s="95" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J31" s="96" t="inlineStr">
         <is>
-          <t>2-3-6</t>
+          <t>4-1-8</t>
         </is>
       </c>
       <c r="K31" s="97" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="L31" s="51" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N31" s="7" t="n"/>
     </row>
@@ -2182,18 +2182,18 @@
         </is>
       </c>
       <c r="I33" s="89" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J33" s="90" t="inlineStr">
         <is>
-          <t>2-2-7</t>
+          <t>3-3-7</t>
         </is>
       </c>
       <c r="K33" s="91" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L33" s="49" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N33" s="7" t="n"/>
     </row>
@@ -2224,18 +2224,18 @@
         </is>
       </c>
       <c r="I35" s="101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J35" s="102" t="inlineStr">
         <is>
-          <t>2-2-8</t>
+          <t>3-2-8</t>
         </is>
       </c>
       <c r="K35" s="103" t="n">
-        <v>-17</v>
+        <v>-16</v>
       </c>
       <c r="L35" s="53" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N35" s="7" t="n"/>
     </row>
@@ -2266,18 +2266,18 @@
         </is>
       </c>
       <c r="I37" s="107" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J37" s="108" t="inlineStr">
         <is>
-          <t>2-1-9</t>
+          <t>2-2-9</t>
         </is>
       </c>
       <c r="K37" s="109" t="n">
         <v>-14</v>
       </c>
       <c r="L37" s="55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N37" s="7" t="n"/>
     </row>
@@ -2308,15 +2308,15 @@
         </is>
       </c>
       <c r="I39" s="107" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J39" s="108" t="inlineStr">
         <is>
-          <t>1-3-7</t>
+          <t>1-3-9</t>
         </is>
       </c>
       <c r="K39" s="109" t="n">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="L39" s="55" t="n">
         <v>6</v>
